--- a/www/terminologies/CodeSystem-terminologie-cisis.xlsx
+++ b/www/terminologies/CodeSystem-terminologie-cisis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4780" uniqueCount="3189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4879" uniqueCount="3255">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>202512170000</t>
+    <t>202603110000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-17T14:37:59-00:00</t>
+    <t>2026-03-11T14:52:01-00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -763,6 +763,12 @@
     <t>Autre complication</t>
   </si>
   <si>
+    <t>GEN-092.01.27</t>
+  </si>
+  <si>
+    <t>Autre facteur de risque</t>
+  </si>
+  <si>
     <t>GEN-092.02.01</t>
   </si>
   <si>
@@ -1051,6 +1057,12 @@
     <t>Autre ressource</t>
   </si>
   <si>
+    <t>GEN-092.06.11</t>
+  </si>
+  <si>
+    <t>Autre collectivité</t>
+  </si>
+  <si>
     <t>GEN-092.07.01</t>
   </si>
   <si>
@@ -2098,12 +2110,6 @@
     <t>Le patient a signé son consentement à la transmission des données au registre ERN cond-GUARD-HEART</t>
   </si>
   <si>
-    <t>GEN-335</t>
-  </si>
-  <si>
-    <t>Le patient a signé son consentement à la transmission des données au registre ERN Heart-Core</t>
-  </si>
-  <si>
     <t>GEN-336</t>
   </si>
   <si>
@@ -2581,6 +2587,96 @@
     <t>Prescriptions</t>
   </si>
   <si>
+    <t>GEN-416</t>
+  </si>
+  <si>
+    <t>Le patient a signé un consentement à la transmission de ses données au registre EuRREB</t>
+  </si>
+  <si>
+    <t>GEN-417</t>
+  </si>
+  <si>
+    <t>Pacsé(e)</t>
+  </si>
+  <si>
+    <t>GEN-418</t>
+  </si>
+  <si>
+    <t>Union libre/Concubinage</t>
+  </si>
+  <si>
+    <t>GEN-419</t>
+  </si>
+  <si>
+    <t>Contact avec un cas de rougeole</t>
+  </si>
+  <si>
+    <t>GEN-420</t>
+  </si>
+  <si>
+    <t>Existence d'autres cas dans l'entourage</t>
+  </si>
+  <si>
+    <t>GEN-421</t>
+  </si>
+  <si>
+    <t>Fréquentation d'une collectivité accueillant des sujets à risque de rougeole grave</t>
+  </si>
+  <si>
+    <t>GEN-422</t>
+  </si>
+  <si>
+    <t>Le patient a signé un consentement à la transmission de ses données au(x) registre(s) de l'ERN GloBE-Reg</t>
+  </si>
+  <si>
+    <t>GEN-423</t>
+  </si>
+  <si>
+    <t>Présence de sujet à risque de rougeole grave dans l’entourage du cas (femme enceinte, immunodéprimé, nourrisson)</t>
+  </si>
+  <si>
+    <t>GEN-424</t>
+  </si>
+  <si>
+    <t>Administration d’immunoglobulines aux contacts à risque de rougeole grave</t>
+  </si>
+  <si>
+    <t>GEN-425</t>
+  </si>
+  <si>
+    <t>Nombre d'admministration d'immunoglobines aux contacts àrisque de rougeole grave</t>
+  </si>
+  <si>
+    <t>GEN-426</t>
+  </si>
+  <si>
+    <t>Administration dans les 72 heures suivant le 1er contact du vaccin ROR aux personnes contact</t>
+  </si>
+  <si>
+    <t>GEN-427</t>
+  </si>
+  <si>
+    <t>Nombre d'administration dans les 72 heures suivant le 1er contact du vaccin ROR aux personnes contact</t>
+  </si>
+  <si>
+    <t>GEN-428</t>
+  </si>
+  <si>
+    <t>Souhaitez-vous recevoir des kits pour prélèvements et envois d’échantillons de salive au CNR (recherche d’IgM/PCR) ?</t>
+  </si>
+  <si>
+    <t>GEN-429</t>
+  </si>
+  <si>
+    <t>Nombre de kits</t>
+  </si>
+  <si>
+    <t>GEN-430</t>
+  </si>
+  <si>
+    <t>Séjour à l’étranger pour les autres cas de rougeole dans l'entourage</t>
+  </si>
+  <si>
     <t>MED-001</t>
   </si>
   <si>
@@ -3037,12 +3133,6 @@
     <t>Décision de prise en soins palliatifs</t>
   </si>
   <si>
-    <t>MED-107</t>
-  </si>
-  <si>
-    <t>Implant</t>
-  </si>
-  <si>
     <t>MED-110</t>
   </si>
   <si>
@@ -4081,13 +4171,13 @@
     <t>MED-363</t>
   </si>
   <si>
-    <t>Hémorragie sévère (manifeste ou récente) ; maladie connue favorisant les hémorragies ; rétinopathie hémorragique (diabétique par ex)</t>
+    <t>Hémorragie sévère (manifeste ou récente), maladie connue favorisant les hémorragies, rétinopathie hémorragique (diabétique par ex)</t>
   </si>
   <si>
     <t>MED-364</t>
   </si>
   <si>
-    <t>Hépatopathie sévère ; pancréatite aiguë</t>
+    <t>Hépatopathie sévère, pancréatite aiguë</t>
   </si>
   <si>
     <t>MED-365</t>
@@ -8395,6 +8485,84 @@
     <t>Médicament diminuant l’INR</t>
   </si>
   <si>
+    <t>MED-1337</t>
+  </si>
+  <si>
+    <t>Le patient (ou le tiers) est-il informé du diagnostic ?</t>
+  </si>
+  <si>
+    <t>MED-1338</t>
+  </si>
+  <si>
+    <t>L'état clinique du patient lui permet-il de répondre à l'investigation ?</t>
+  </si>
+  <si>
+    <t>MED-1339</t>
+  </si>
+  <si>
+    <t>Complication</t>
+  </si>
+  <si>
+    <t>MED-1340</t>
+  </si>
+  <si>
+    <t>Vaccination autre flavivirus</t>
+  </si>
+  <si>
+    <t>MED-1341</t>
+  </si>
+  <si>
+    <t>Autre(s) exposition(s)</t>
+  </si>
+  <si>
+    <t>MED-1342</t>
+  </si>
+  <si>
+    <t>Questionnaire ICOPE 60-65 ans</t>
+  </si>
+  <si>
+    <t>MED-1343</t>
+  </si>
+  <si>
+    <t>Questionnaire ICOPE 66-69 ans</t>
+  </si>
+  <si>
+    <t>MED-1344</t>
+  </si>
+  <si>
+    <t>Questionnaire ICOPE 70-75 ans</t>
+  </si>
+  <si>
+    <t>MED-1345</t>
+  </si>
+  <si>
+    <t>Questionnaire ICOPE 76 ans et plus</t>
+  </si>
+  <si>
+    <t>MED-1346</t>
+  </si>
+  <si>
+    <t>Questionnaire Mon Bilan Prévention 18-25 ans</t>
+  </si>
+  <si>
+    <t>MED-1347</t>
+  </si>
+  <si>
+    <t>Questionnaire Mon Bilan Prévention 45-50 ans</t>
+  </si>
+  <si>
+    <t>MED-1348</t>
+  </si>
+  <si>
+    <t>Questionnaire Mon Bilan Prévention 60-65 ans</t>
+  </si>
+  <si>
+    <t>MED-1349</t>
+  </si>
+  <si>
+    <t>Questionnaire Mon Bilan Prévention 70-75 ans</t>
+  </si>
+  <si>
     <t>ORG-001</t>
   </si>
   <si>
@@ -9269,6 +9437,36 @@
   </si>
   <si>
     <t>Intervenant à domicile</t>
+  </si>
+  <si>
+    <t>ORG-225</t>
+  </si>
+  <si>
+    <t>RCP Métastase osseuse</t>
+  </si>
+  <si>
+    <t>ORG-226</t>
+  </si>
+  <si>
+    <t>RCP Cancers rares</t>
+  </si>
+  <si>
+    <t>ORG-227</t>
+  </si>
+  <si>
+    <t>Domicile ou milieu ordinaire</t>
+  </si>
+  <si>
+    <t>ORG-228</t>
+  </si>
+  <si>
+    <t>Etablissement médico-social</t>
+  </si>
+  <si>
+    <t>ORG-229</t>
+  </si>
+  <si>
+    <t>Provenance inconnue</t>
   </si>
   <si>
     <t>PAT-001</t>
@@ -9982,7 +10180,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1573"/>
+  <dimension ref="A1:D1606"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -12443,7 +12641,7 @@
         <v>463</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>37</v>
+        <v>464</v>
       </c>
       <c r="D205" s="2"/>
     </row>
@@ -12452,10 +12650,10 @@
         <v>57</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="D206" s="2"/>
     </row>
@@ -12464,10 +12662,10 @@
         <v>57</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>467</v>
+        <v>37</v>
       </c>
       <c r="D207" s="2"/>
     </row>
@@ -14267,7 +14465,7 @@
         <v>766</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>93</v>
+        <v>767</v>
       </c>
       <c r="D357" s="2"/>
     </row>
@@ -14276,10 +14474,10 @@
         <v>57</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>768</v>
+        <v>93</v>
       </c>
       <c r="D358" s="2"/>
     </row>
@@ -16427,7 +16625,7 @@
         <v>1125</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>200</v>
+        <v>1126</v>
       </c>
       <c r="D537" s="2"/>
     </row>
@@ -16436,10 +16634,10 @@
         <v>57</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="D538" s="2"/>
     </row>
@@ -16448,10 +16646,10 @@
         <v>57</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D539" s="2"/>
     </row>
@@ -16460,10 +16658,10 @@
         <v>57</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D540" s="2"/>
     </row>
@@ -16472,10 +16670,10 @@
         <v>57</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="D541" s="2"/>
     </row>
@@ -16484,10 +16682,10 @@
         <v>57</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="D542" s="2"/>
     </row>
@@ -16496,10 +16694,10 @@
         <v>57</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D543" s="2"/>
     </row>
@@ -16508,10 +16706,10 @@
         <v>57</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D544" s="2"/>
     </row>
@@ -16520,10 +16718,10 @@
         <v>57</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="D545" s="2"/>
     </row>
@@ -16532,10 +16730,10 @@
         <v>57</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="D546" s="2"/>
     </row>
@@ -16544,10 +16742,10 @@
         <v>57</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="D547" s="2"/>
     </row>
@@ -16556,10 +16754,10 @@
         <v>57</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D548" s="2"/>
     </row>
@@ -16568,10 +16766,10 @@
         <v>57</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="D549" s="2"/>
     </row>
@@ -16580,10 +16778,10 @@
         <v>57</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="D550" s="2"/>
     </row>
@@ -16592,10 +16790,10 @@
         <v>57</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="D551" s="2"/>
     </row>
@@ -16604,10 +16802,10 @@
         <v>57</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1155</v>
+        <v>200</v>
       </c>
       <c r="D552" s="2"/>
     </row>
@@ -21059,7 +21257,7 @@
         <v>1896</v>
       </c>
       <c r="C923" t="s" s="2">
-        <v>565</v>
+        <v>1897</v>
       </c>
       <c r="D923" s="2"/>
     </row>
@@ -21068,10 +21266,10 @@
         <v>57</v>
       </c>
       <c r="B924" t="s" s="2">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="C924" t="s" s="2">
-        <v>567</v>
+        <v>1899</v>
       </c>
       <c r="D924" s="2"/>
     </row>
@@ -21080,10 +21278,10 @@
         <v>57</v>
       </c>
       <c r="B925" t="s" s="2">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="C925" t="s" s="2">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="D925" s="2"/>
     </row>
@@ -21092,10 +21290,10 @@
         <v>57</v>
       </c>
       <c r="B926" t="s" s="2">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="C926" t="s" s="2">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="D926" s="2"/>
     </row>
@@ -21104,10 +21302,10 @@
         <v>57</v>
       </c>
       <c r="B927" t="s" s="2">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="C927" t="s" s="2">
-        <v>1903</v>
+        <v>1905</v>
       </c>
       <c r="D927" s="2"/>
     </row>
@@ -21116,10 +21314,10 @@
         <v>57</v>
       </c>
       <c r="B928" t="s" s="2">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="C928" t="s" s="2">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="D928" s="2"/>
     </row>
@@ -21128,10 +21326,10 @@
         <v>57</v>
       </c>
       <c r="B929" t="s" s="2">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="C929" t="s" s="2">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="D929" s="2"/>
     </row>
@@ -21140,10 +21338,10 @@
         <v>57</v>
       </c>
       <c r="B930" t="s" s="2">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="C930" t="s" s="2">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="D930" s="2"/>
     </row>
@@ -21152,10 +21350,10 @@
         <v>57</v>
       </c>
       <c r="B931" t="s" s="2">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="C931" t="s" s="2">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="D931" s="2"/>
     </row>
@@ -21164,10 +21362,10 @@
         <v>57</v>
       </c>
       <c r="B932" t="s" s="2">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="C932" t="s" s="2">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="D932" s="2"/>
     </row>
@@ -21176,10 +21374,10 @@
         <v>57</v>
       </c>
       <c r="B933" t="s" s="2">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="C933" t="s" s="2">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="D933" s="2"/>
     </row>
@@ -21188,10 +21386,10 @@
         <v>57</v>
       </c>
       <c r="B934" t="s" s="2">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="C934" t="s" s="2">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="D934" s="2"/>
     </row>
@@ -21200,10 +21398,10 @@
         <v>57</v>
       </c>
       <c r="B935" t="s" s="2">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="C935" t="s" s="2">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="D935" s="2"/>
     </row>
@@ -21212,10 +21410,10 @@
         <v>57</v>
       </c>
       <c r="B936" t="s" s="2">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="C936" t="s" s="2">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="D936" s="2"/>
     </row>
@@ -21224,10 +21422,10 @@
         <v>57</v>
       </c>
       <c r="B937" t="s" s="2">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="C937" t="s" s="2">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="D937" s="2"/>
     </row>
@@ -21236,10 +21434,10 @@
         <v>57</v>
       </c>
       <c r="B938" t="s" s="2">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="C938" t="s" s="2">
-        <v>1925</v>
+        <v>569</v>
       </c>
       <c r="D938" s="2"/>
     </row>
@@ -21248,10 +21446,10 @@
         <v>57</v>
       </c>
       <c r="B939" t="s" s="2">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="C939" t="s" s="2">
-        <v>1927</v>
+        <v>571</v>
       </c>
       <c r="D939" s="2"/>
     </row>
@@ -21599,7 +21797,7 @@
         <v>1984</v>
       </c>
       <c r="C968" t="s" s="2">
-        <v>1939</v>
+        <v>1985</v>
       </c>
       <c r="D968" s="2"/>
     </row>
@@ -21608,10 +21806,10 @@
         <v>57</v>
       </c>
       <c r="B969" t="s" s="2">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="C969" t="s" s="2">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="D969" s="2"/>
     </row>
@@ -21620,10 +21818,10 @@
         <v>57</v>
       </c>
       <c r="B970" t="s" s="2">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="C970" t="s" s="2">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="D970" s="2"/>
     </row>
@@ -21632,10 +21830,10 @@
         <v>57</v>
       </c>
       <c r="B971" t="s" s="2">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="C971" t="s" s="2">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="D971" s="2"/>
     </row>
@@ -21644,10 +21842,10 @@
         <v>57</v>
       </c>
       <c r="B972" t="s" s="2">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="C972" t="s" s="2">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="D972" s="2"/>
     </row>
@@ -21656,10 +21854,10 @@
         <v>57</v>
       </c>
       <c r="B973" t="s" s="2">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="C973" t="s" s="2">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="D973" s="2"/>
     </row>
@@ -21668,10 +21866,10 @@
         <v>57</v>
       </c>
       <c r="B974" t="s" s="2">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="C974" t="s" s="2">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="D974" s="2"/>
     </row>
@@ -21680,10 +21878,10 @@
         <v>57</v>
       </c>
       <c r="B975" t="s" s="2">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C975" t="s" s="2">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="D975" s="2"/>
     </row>
@@ -21692,10 +21890,10 @@
         <v>57</v>
       </c>
       <c r="B976" t="s" s="2">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="C976" t="s" s="2">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="D976" s="2"/>
     </row>
@@ -21704,10 +21902,10 @@
         <v>57</v>
       </c>
       <c r="B977" t="s" s="2">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="C977" t="s" s="2">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="D977" s="2"/>
     </row>
@@ -21716,10 +21914,10 @@
         <v>57</v>
       </c>
       <c r="B978" t="s" s="2">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C978" t="s" s="2">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D978" s="2"/>
     </row>
@@ -21728,10 +21926,10 @@
         <v>57</v>
       </c>
       <c r="B979" t="s" s="2">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="C979" t="s" s="2">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="D979" s="2"/>
     </row>
@@ -21740,10 +21938,10 @@
         <v>57</v>
       </c>
       <c r="B980" t="s" s="2">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="C980" t="s" s="2">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="D980" s="2"/>
     </row>
@@ -21752,10 +21950,10 @@
         <v>57</v>
       </c>
       <c r="B981" t="s" s="2">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="C981" t="s" s="2">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D981" s="2"/>
     </row>
@@ -21764,10 +21962,10 @@
         <v>57</v>
       </c>
       <c r="B982" t="s" s="2">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="C982" t="s" s="2">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="D982" s="2"/>
     </row>
@@ -21776,10 +21974,10 @@
         <v>57</v>
       </c>
       <c r="B983" t="s" s="2">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="C983" t="s" s="2">
-        <v>2014</v>
+        <v>1969</v>
       </c>
       <c r="D983" s="2"/>
     </row>
@@ -23171,7 +23369,7 @@
         <v>2245</v>
       </c>
       <c r="C1099" t="s" s="2">
-        <v>2194</v>
+        <v>2246</v>
       </c>
       <c r="D1099" s="2"/>
     </row>
@@ -23180,10 +23378,10 @@
         <v>57</v>
       </c>
       <c r="B1100" t="s" s="2">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="C1100" t="s" s="2">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="D1100" s="2"/>
     </row>
@@ -23192,10 +23390,10 @@
         <v>57</v>
       </c>
       <c r="B1101" t="s" s="2">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="C1101" t="s" s="2">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="D1101" s="2"/>
     </row>
@@ -23204,10 +23402,10 @@
         <v>57</v>
       </c>
       <c r="B1102" t="s" s="2">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="C1102" t="s" s="2">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="D1102" s="2"/>
     </row>
@@ -23216,10 +23414,10 @@
         <v>57</v>
       </c>
       <c r="B1103" t="s" s="2">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="C1103" t="s" s="2">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="D1103" s="2"/>
     </row>
@@ -23228,10 +23426,10 @@
         <v>57</v>
       </c>
       <c r="B1104" t="s" s="2">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="C1104" t="s" s="2">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="D1104" s="2"/>
     </row>
@@ -23240,10 +23438,10 @@
         <v>57</v>
       </c>
       <c r="B1105" t="s" s="2">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="C1105" t="s" s="2">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="D1105" s="2"/>
     </row>
@@ -23252,10 +23450,10 @@
         <v>57</v>
       </c>
       <c r="B1106" t="s" s="2">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="C1106" t="s" s="2">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="D1106" s="2"/>
     </row>
@@ -23264,10 +23462,10 @@
         <v>57</v>
       </c>
       <c r="B1107" t="s" s="2">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="C1107" t="s" s="2">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="D1107" s="2"/>
     </row>
@@ -23276,10 +23474,10 @@
         <v>57</v>
       </c>
       <c r="B1108" t="s" s="2">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="C1108" t="s" s="2">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="D1108" s="2"/>
     </row>
@@ -23288,10 +23486,10 @@
         <v>57</v>
       </c>
       <c r="B1109" t="s" s="2">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C1109" t="s" s="2">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="D1109" s="2"/>
     </row>
@@ -23300,10 +23498,10 @@
         <v>57</v>
       </c>
       <c r="B1110" t="s" s="2">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="C1110" t="s" s="2">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="D1110" s="2"/>
     </row>
@@ -23312,10 +23510,10 @@
         <v>57</v>
       </c>
       <c r="B1111" t="s" s="2">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="C1111" t="s" s="2">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="D1111" s="2"/>
     </row>
@@ -23324,10 +23522,10 @@
         <v>57</v>
       </c>
       <c r="B1112" t="s" s="2">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="C1112" t="s" s="2">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="D1112" s="2"/>
     </row>
@@ -23336,10 +23534,10 @@
         <v>57</v>
       </c>
       <c r="B1113" t="s" s="2">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="C1113" t="s" s="2">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="D1113" s="2"/>
     </row>
@@ -23348,10 +23546,10 @@
         <v>57</v>
       </c>
       <c r="B1114" t="s" s="2">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="C1114" t="s" s="2">
-        <v>2275</v>
+        <v>2224</v>
       </c>
       <c r="D1114" s="2"/>
     </row>
@@ -25451,7 +25649,7 @@
         <v>2624</v>
       </c>
       <c r="C1289" t="s" s="2">
-        <v>2577</v>
+        <v>2625</v>
       </c>
       <c r="D1289" s="2"/>
     </row>
@@ -25460,10 +25658,10 @@
         <v>57</v>
       </c>
       <c r="B1290" t="s" s="2">
-        <v>2625</v>
+        <v>2626</v>
       </c>
       <c r="C1290" t="s" s="2">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="D1290" s="2"/>
     </row>
@@ -25472,10 +25670,10 @@
         <v>57</v>
       </c>
       <c r="B1291" t="s" s="2">
-        <v>2627</v>
+        <v>2628</v>
       </c>
       <c r="C1291" t="s" s="2">
-        <v>2628</v>
+        <v>2629</v>
       </c>
       <c r="D1291" s="2"/>
     </row>
@@ -25484,10 +25682,10 @@
         <v>57</v>
       </c>
       <c r="B1292" t="s" s="2">
-        <v>2629</v>
+        <v>2630</v>
       </c>
       <c r="C1292" t="s" s="2">
-        <v>2630</v>
+        <v>2631</v>
       </c>
       <c r="D1292" s="2"/>
     </row>
@@ -25496,10 +25694,10 @@
         <v>57</v>
       </c>
       <c r="B1293" t="s" s="2">
-        <v>2631</v>
+        <v>2632</v>
       </c>
       <c r="C1293" t="s" s="2">
-        <v>2632</v>
+        <v>2633</v>
       </c>
       <c r="D1293" s="2"/>
     </row>
@@ -25508,10 +25706,10 @@
         <v>57</v>
       </c>
       <c r="B1294" t="s" s="2">
-        <v>2633</v>
+        <v>2634</v>
       </c>
       <c r="C1294" t="s" s="2">
-        <v>2634</v>
+        <v>2635</v>
       </c>
       <c r="D1294" s="2"/>
     </row>
@@ -25520,10 +25718,10 @@
         <v>57</v>
       </c>
       <c r="B1295" t="s" s="2">
-        <v>2635</v>
+        <v>2636</v>
       </c>
       <c r="C1295" t="s" s="2">
-        <v>2636</v>
+        <v>2637</v>
       </c>
       <c r="D1295" s="2"/>
     </row>
@@ -25532,10 +25730,10 @@
         <v>57</v>
       </c>
       <c r="B1296" t="s" s="2">
-        <v>2637</v>
+        <v>2638</v>
       </c>
       <c r="C1296" t="s" s="2">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="D1296" s="2"/>
     </row>
@@ -25544,10 +25742,10 @@
         <v>57</v>
       </c>
       <c r="B1297" t="s" s="2">
-        <v>2639</v>
+        <v>2640</v>
       </c>
       <c r="C1297" t="s" s="2">
-        <v>2640</v>
+        <v>2641</v>
       </c>
       <c r="D1297" s="2"/>
     </row>
@@ -25556,10 +25754,10 @@
         <v>57</v>
       </c>
       <c r="B1298" t="s" s="2">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="C1298" t="s" s="2">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="D1298" s="2"/>
     </row>
@@ -25568,10 +25766,10 @@
         <v>57</v>
       </c>
       <c r="B1299" t="s" s="2">
-        <v>2643</v>
+        <v>2644</v>
       </c>
       <c r="C1299" t="s" s="2">
-        <v>2644</v>
+        <v>2645</v>
       </c>
       <c r="D1299" s="2"/>
     </row>
@@ -25580,10 +25778,10 @@
         <v>57</v>
       </c>
       <c r="B1300" t="s" s="2">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="C1300" t="s" s="2">
-        <v>2646</v>
+        <v>2647</v>
       </c>
       <c r="D1300" s="2"/>
     </row>
@@ -25592,10 +25790,10 @@
         <v>57</v>
       </c>
       <c r="B1301" t="s" s="2">
-        <v>2647</v>
+        <v>2648</v>
       </c>
       <c r="C1301" t="s" s="2">
-        <v>2648</v>
+        <v>2649</v>
       </c>
       <c r="D1301" s="2"/>
     </row>
@@ -25604,10 +25802,10 @@
         <v>57</v>
       </c>
       <c r="B1302" t="s" s="2">
-        <v>2649</v>
+        <v>2650</v>
       </c>
       <c r="C1302" t="s" s="2">
-        <v>2650</v>
+        <v>2651</v>
       </c>
       <c r="D1302" s="2"/>
     </row>
@@ -25616,10 +25814,10 @@
         <v>57</v>
       </c>
       <c r="B1303" t="s" s="2">
-        <v>2651</v>
+        <v>2652</v>
       </c>
       <c r="C1303" t="s" s="2">
-        <v>2652</v>
+        <v>2653</v>
       </c>
       <c r="D1303" s="2"/>
     </row>
@@ -25628,10 +25826,10 @@
         <v>57</v>
       </c>
       <c r="B1304" t="s" s="2">
-        <v>2653</v>
+        <v>2654</v>
       </c>
       <c r="C1304" t="s" s="2">
-        <v>2654</v>
+        <v>2607</v>
       </c>
       <c r="D1304" s="2"/>
     </row>
@@ -25907,7 +26105,7 @@
         <v>2699</v>
       </c>
       <c r="C1327" t="s" s="2">
-        <v>298</v>
+        <v>2700</v>
       </c>
       <c r="D1327" s="2"/>
     </row>
@@ -25916,10 +26114,10 @@
         <v>57</v>
       </c>
       <c r="B1328" t="s" s="2">
-        <v>2700</v>
+        <v>2701</v>
       </c>
       <c r="C1328" t="s" s="2">
-        <v>2701</v>
+        <v>2702</v>
       </c>
       <c r="D1328" s="2"/>
     </row>
@@ -25928,10 +26126,10 @@
         <v>57</v>
       </c>
       <c r="B1329" t="s" s="2">
-        <v>2702</v>
+        <v>2703</v>
       </c>
       <c r="C1329" t="s" s="2">
-        <v>2703</v>
+        <v>2704</v>
       </c>
       <c r="D1329" s="2"/>
     </row>
@@ -25940,10 +26138,10 @@
         <v>57</v>
       </c>
       <c r="B1330" t="s" s="2">
-        <v>2704</v>
+        <v>2705</v>
       </c>
       <c r="C1330" t="s" s="2">
-        <v>2705</v>
+        <v>2706</v>
       </c>
       <c r="D1330" s="2"/>
     </row>
@@ -25952,10 +26150,10 @@
         <v>57</v>
       </c>
       <c r="B1331" t="s" s="2">
-        <v>2706</v>
+        <v>2707</v>
       </c>
       <c r="C1331" t="s" s="2">
-        <v>2707</v>
+        <v>2708</v>
       </c>
       <c r="D1331" s="2"/>
     </row>
@@ -25964,10 +26162,10 @@
         <v>57</v>
       </c>
       <c r="B1332" t="s" s="2">
-        <v>2708</v>
+        <v>2709</v>
       </c>
       <c r="C1332" t="s" s="2">
-        <v>2709</v>
+        <v>2710</v>
       </c>
       <c r="D1332" s="2"/>
     </row>
@@ -25976,10 +26174,10 @@
         <v>57</v>
       </c>
       <c r="B1333" t="s" s="2">
-        <v>2710</v>
+        <v>2711</v>
       </c>
       <c r="C1333" t="s" s="2">
-        <v>2711</v>
+        <v>2712</v>
       </c>
       <c r="D1333" s="2"/>
     </row>
@@ -25988,10 +26186,10 @@
         <v>57</v>
       </c>
       <c r="B1334" t="s" s="2">
-        <v>2712</v>
+        <v>2713</v>
       </c>
       <c r="C1334" t="s" s="2">
-        <v>2713</v>
+        <v>2714</v>
       </c>
       <c r="D1334" s="2"/>
     </row>
@@ -26000,10 +26198,10 @@
         <v>57</v>
       </c>
       <c r="B1335" t="s" s="2">
-        <v>2714</v>
+        <v>2715</v>
       </c>
       <c r="C1335" t="s" s="2">
-        <v>2715</v>
+        <v>2716</v>
       </c>
       <c r="D1335" s="2"/>
     </row>
@@ -26012,10 +26210,10 @@
         <v>57</v>
       </c>
       <c r="B1336" t="s" s="2">
-        <v>2716</v>
+        <v>2717</v>
       </c>
       <c r="C1336" t="s" s="2">
-        <v>2717</v>
+        <v>2718</v>
       </c>
       <c r="D1336" s="2"/>
     </row>
@@ -26024,10 +26222,10 @@
         <v>57</v>
       </c>
       <c r="B1337" t="s" s="2">
-        <v>2718</v>
+        <v>2719</v>
       </c>
       <c r="C1337" t="s" s="2">
-        <v>2719</v>
+        <v>2720</v>
       </c>
       <c r="D1337" s="2"/>
     </row>
@@ -26036,10 +26234,10 @@
         <v>57</v>
       </c>
       <c r="B1338" t="s" s="2">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="C1338" t="s" s="2">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="D1338" s="2"/>
     </row>
@@ -26048,10 +26246,10 @@
         <v>57</v>
       </c>
       <c r="B1339" t="s" s="2">
-        <v>2722</v>
+        <v>2723</v>
       </c>
       <c r="C1339" t="s" s="2">
-        <v>2723</v>
+        <v>2724</v>
       </c>
       <c r="D1339" s="2"/>
     </row>
@@ -26060,10 +26258,10 @@
         <v>57</v>
       </c>
       <c r="B1340" t="s" s="2">
-        <v>2724</v>
+        <v>2725</v>
       </c>
       <c r="C1340" t="s" s="2">
-        <v>59</v>
+        <v>2726</v>
       </c>
       <c r="D1340" s="2"/>
     </row>
@@ -26072,10 +26270,10 @@
         <v>57</v>
       </c>
       <c r="B1341" t="s" s="2">
-        <v>2725</v>
+        <v>2727</v>
       </c>
       <c r="C1341" t="s" s="2">
-        <v>61</v>
+        <v>2728</v>
       </c>
       <c r="D1341" s="2"/>
     </row>
@@ -26084,10 +26282,10 @@
         <v>57</v>
       </c>
       <c r="B1342" t="s" s="2">
-        <v>2726</v>
+        <v>2729</v>
       </c>
       <c r="C1342" t="s" s="2">
-        <v>63</v>
+        <v>300</v>
       </c>
       <c r="D1342" s="2"/>
     </row>
@@ -26096,10 +26294,10 @@
         <v>57</v>
       </c>
       <c r="B1343" t="s" s="2">
-        <v>2727</v>
+        <v>2730</v>
       </c>
       <c r="C1343" t="s" s="2">
-        <v>2728</v>
+        <v>2731</v>
       </c>
       <c r="D1343" s="2"/>
     </row>
@@ -26108,10 +26306,10 @@
         <v>57</v>
       </c>
       <c r="B1344" t="s" s="2">
-        <v>2729</v>
+        <v>2732</v>
       </c>
       <c r="C1344" t="s" s="2">
-        <v>2730</v>
+        <v>2733</v>
       </c>
       <c r="D1344" s="2"/>
     </row>
@@ -26120,10 +26318,10 @@
         <v>57</v>
       </c>
       <c r="B1345" t="s" s="2">
-        <v>2731</v>
+        <v>2734</v>
       </c>
       <c r="C1345" t="s" s="2">
-        <v>2732</v>
+        <v>2735</v>
       </c>
       <c r="D1345" s="2"/>
     </row>
@@ -26132,10 +26330,10 @@
         <v>57</v>
       </c>
       <c r="B1346" t="s" s="2">
-        <v>2733</v>
+        <v>2736</v>
       </c>
       <c r="C1346" t="s" s="2">
-        <v>2734</v>
+        <v>2737</v>
       </c>
       <c r="D1346" s="2"/>
     </row>
@@ -26144,10 +26342,10 @@
         <v>57</v>
       </c>
       <c r="B1347" t="s" s="2">
-        <v>2735</v>
+        <v>2738</v>
       </c>
       <c r="C1347" t="s" s="2">
-        <v>2736</v>
+        <v>2739</v>
       </c>
       <c r="D1347" s="2"/>
     </row>
@@ -26156,10 +26354,10 @@
         <v>57</v>
       </c>
       <c r="B1348" t="s" s="2">
-        <v>2737</v>
+        <v>2740</v>
       </c>
       <c r="C1348" t="s" s="2">
-        <v>2738</v>
+        <v>2741</v>
       </c>
       <c r="D1348" s="2"/>
     </row>
@@ -26168,10 +26366,10 @@
         <v>57</v>
       </c>
       <c r="B1349" t="s" s="2">
-        <v>2739</v>
+        <v>2742</v>
       </c>
       <c r="C1349" t="s" s="2">
-        <v>2740</v>
+        <v>2743</v>
       </c>
       <c r="D1349" s="2"/>
     </row>
@@ -26180,10 +26378,10 @@
         <v>57</v>
       </c>
       <c r="B1350" t="s" s="2">
-        <v>2741</v>
+        <v>2744</v>
       </c>
       <c r="C1350" t="s" s="2">
-        <v>2742</v>
+        <v>2745</v>
       </c>
       <c r="D1350" s="2"/>
     </row>
@@ -26192,10 +26390,10 @@
         <v>57</v>
       </c>
       <c r="B1351" t="s" s="2">
-        <v>2743</v>
+        <v>2746</v>
       </c>
       <c r="C1351" t="s" s="2">
-        <v>2744</v>
+        <v>2747</v>
       </c>
       <c r="D1351" s="2"/>
     </row>
@@ -26204,10 +26402,10 @@
         <v>57</v>
       </c>
       <c r="B1352" t="s" s="2">
-        <v>2745</v>
+        <v>2748</v>
       </c>
       <c r="C1352" t="s" s="2">
-        <v>2746</v>
+        <v>2749</v>
       </c>
       <c r="D1352" s="2"/>
     </row>
@@ -26216,10 +26414,10 @@
         <v>57</v>
       </c>
       <c r="B1353" t="s" s="2">
-        <v>2747</v>
+        <v>2750</v>
       </c>
       <c r="C1353" t="s" s="2">
-        <v>2748</v>
+        <v>2751</v>
       </c>
       <c r="D1353" s="2"/>
     </row>
@@ -26228,10 +26426,10 @@
         <v>57</v>
       </c>
       <c r="B1354" t="s" s="2">
-        <v>2749</v>
+        <v>2752</v>
       </c>
       <c r="C1354" t="s" s="2">
-        <v>2750</v>
+        <v>2753</v>
       </c>
       <c r="D1354" s="2"/>
     </row>
@@ -26240,10 +26438,10 @@
         <v>57</v>
       </c>
       <c r="B1355" t="s" s="2">
-        <v>2751</v>
+        <v>2754</v>
       </c>
       <c r="C1355" t="s" s="2">
-        <v>2752</v>
+        <v>59</v>
       </c>
       <c r="D1355" s="2"/>
     </row>
@@ -26252,10 +26450,10 @@
         <v>57</v>
       </c>
       <c r="B1356" t="s" s="2">
-        <v>2753</v>
+        <v>2755</v>
       </c>
       <c r="C1356" t="s" s="2">
-        <v>2754</v>
+        <v>61</v>
       </c>
       <c r="D1356" s="2"/>
     </row>
@@ -26264,10 +26462,10 @@
         <v>57</v>
       </c>
       <c r="B1357" t="s" s="2">
-        <v>2755</v>
+        <v>2756</v>
       </c>
       <c r="C1357" t="s" s="2">
-        <v>2756</v>
+        <v>63</v>
       </c>
       <c r="D1357" s="2"/>
     </row>
@@ -28862,6 +29060,402 @@
         <v>3188</v>
       </c>
       <c r="D1573" s="2"/>
+    </row>
+    <row r="1574">
+      <c r="A1574" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1574" t="s" s="2">
+        <v>3189</v>
+      </c>
+      <c r="C1574" t="s" s="2">
+        <v>3190</v>
+      </c>
+      <c r="D1574" s="2"/>
+    </row>
+    <row r="1575">
+      <c r="A1575" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1575" t="s" s="2">
+        <v>3191</v>
+      </c>
+      <c r="C1575" t="s" s="2">
+        <v>3192</v>
+      </c>
+      <c r="D1575" s="2"/>
+    </row>
+    <row r="1576">
+      <c r="A1576" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1576" t="s" s="2">
+        <v>3193</v>
+      </c>
+      <c r="C1576" t="s" s="2">
+        <v>3194</v>
+      </c>
+      <c r="D1576" s="2"/>
+    </row>
+    <row r="1577">
+      <c r="A1577" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1577" t="s" s="2">
+        <v>3195</v>
+      </c>
+      <c r="C1577" t="s" s="2">
+        <v>3196</v>
+      </c>
+      <c r="D1577" s="2"/>
+    </row>
+    <row r="1578">
+      <c r="A1578" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1578" t="s" s="2">
+        <v>3197</v>
+      </c>
+      <c r="C1578" t="s" s="2">
+        <v>3198</v>
+      </c>
+      <c r="D1578" s="2"/>
+    </row>
+    <row r="1579">
+      <c r="A1579" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1579" t="s" s="2">
+        <v>3199</v>
+      </c>
+      <c r="C1579" t="s" s="2">
+        <v>3200</v>
+      </c>
+      <c r="D1579" s="2"/>
+    </row>
+    <row r="1580">
+      <c r="A1580" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1580" t="s" s="2">
+        <v>3201</v>
+      </c>
+      <c r="C1580" t="s" s="2">
+        <v>3202</v>
+      </c>
+      <c r="D1580" s="2"/>
+    </row>
+    <row r="1581">
+      <c r="A1581" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1581" t="s" s="2">
+        <v>3203</v>
+      </c>
+      <c r="C1581" t="s" s="2">
+        <v>3204</v>
+      </c>
+      <c r="D1581" s="2"/>
+    </row>
+    <row r="1582">
+      <c r="A1582" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1582" t="s" s="2">
+        <v>3205</v>
+      </c>
+      <c r="C1582" t="s" s="2">
+        <v>3206</v>
+      </c>
+      <c r="D1582" s="2"/>
+    </row>
+    <row r="1583">
+      <c r="A1583" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1583" t="s" s="2">
+        <v>3207</v>
+      </c>
+      <c r="C1583" t="s" s="2">
+        <v>3208</v>
+      </c>
+      <c r="D1583" s="2"/>
+    </row>
+    <row r="1584">
+      <c r="A1584" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1584" t="s" s="2">
+        <v>3209</v>
+      </c>
+      <c r="C1584" t="s" s="2">
+        <v>3210</v>
+      </c>
+      <c r="D1584" s="2"/>
+    </row>
+    <row r="1585">
+      <c r="A1585" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1585" t="s" s="2">
+        <v>3211</v>
+      </c>
+      <c r="C1585" t="s" s="2">
+        <v>3212</v>
+      </c>
+      <c r="D1585" s="2"/>
+    </row>
+    <row r="1586">
+      <c r="A1586" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1586" t="s" s="2">
+        <v>3213</v>
+      </c>
+      <c r="C1586" t="s" s="2">
+        <v>3214</v>
+      </c>
+      <c r="D1586" s="2"/>
+    </row>
+    <row r="1587">
+      <c r="A1587" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1587" t="s" s="2">
+        <v>3215</v>
+      </c>
+      <c r="C1587" t="s" s="2">
+        <v>3216</v>
+      </c>
+      <c r="D1587" s="2"/>
+    </row>
+    <row r="1588">
+      <c r="A1588" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1588" t="s" s="2">
+        <v>3217</v>
+      </c>
+      <c r="C1588" t="s" s="2">
+        <v>3218</v>
+      </c>
+      <c r="D1588" s="2"/>
+    </row>
+    <row r="1589">
+      <c r="A1589" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1589" t="s" s="2">
+        <v>3219</v>
+      </c>
+      <c r="C1589" t="s" s="2">
+        <v>3220</v>
+      </c>
+      <c r="D1589" s="2"/>
+    </row>
+    <row r="1590">
+      <c r="A1590" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1590" t="s" s="2">
+        <v>3221</v>
+      </c>
+      <c r="C1590" t="s" s="2">
+        <v>3222</v>
+      </c>
+      <c r="D1590" s="2"/>
+    </row>
+    <row r="1591">
+      <c r="A1591" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1591" t="s" s="2">
+        <v>3223</v>
+      </c>
+      <c r="C1591" t="s" s="2">
+        <v>3224</v>
+      </c>
+      <c r="D1591" s="2"/>
+    </row>
+    <row r="1592">
+      <c r="A1592" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1592" t="s" s="2">
+        <v>3225</v>
+      </c>
+      <c r="C1592" t="s" s="2">
+        <v>3226</v>
+      </c>
+      <c r="D1592" s="2"/>
+    </row>
+    <row r="1593">
+      <c r="A1593" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1593" t="s" s="2">
+        <v>3227</v>
+      </c>
+      <c r="C1593" t="s" s="2">
+        <v>3228</v>
+      </c>
+      <c r="D1593" s="2"/>
+    </row>
+    <row r="1594">
+      <c r="A1594" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1594" t="s" s="2">
+        <v>3229</v>
+      </c>
+      <c r="C1594" t="s" s="2">
+        <v>3230</v>
+      </c>
+      <c r="D1594" s="2"/>
+    </row>
+    <row r="1595">
+      <c r="A1595" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1595" t="s" s="2">
+        <v>3231</v>
+      </c>
+      <c r="C1595" t="s" s="2">
+        <v>3232</v>
+      </c>
+      <c r="D1595" s="2"/>
+    </row>
+    <row r="1596">
+      <c r="A1596" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1596" t="s" s="2">
+        <v>3233</v>
+      </c>
+      <c r="C1596" t="s" s="2">
+        <v>3234</v>
+      </c>
+      <c r="D1596" s="2"/>
+    </row>
+    <row r="1597">
+      <c r="A1597" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1597" t="s" s="2">
+        <v>3235</v>
+      </c>
+      <c r="C1597" t="s" s="2">
+        <v>3236</v>
+      </c>
+      <c r="D1597" s="2"/>
+    </row>
+    <row r="1598">
+      <c r="A1598" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1598" t="s" s="2">
+        <v>3237</v>
+      </c>
+      <c r="C1598" t="s" s="2">
+        <v>3238</v>
+      </c>
+      <c r="D1598" s="2"/>
+    </row>
+    <row r="1599">
+      <c r="A1599" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1599" t="s" s="2">
+        <v>3239</v>
+      </c>
+      <c r="C1599" t="s" s="2">
+        <v>3240</v>
+      </c>
+      <c r="D1599" s="2"/>
+    </row>
+    <row r="1600">
+      <c r="A1600" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1600" t="s" s="2">
+        <v>3241</v>
+      </c>
+      <c r="C1600" t="s" s="2">
+        <v>3242</v>
+      </c>
+      <c r="D1600" s="2"/>
+    </row>
+    <row r="1601">
+      <c r="A1601" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1601" t="s" s="2">
+        <v>3243</v>
+      </c>
+      <c r="C1601" t="s" s="2">
+        <v>3244</v>
+      </c>
+      <c r="D1601" s="2"/>
+    </row>
+    <row r="1602">
+      <c r="A1602" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1602" t="s" s="2">
+        <v>3245</v>
+      </c>
+      <c r="C1602" t="s" s="2">
+        <v>3246</v>
+      </c>
+      <c r="D1602" s="2"/>
+    </row>
+    <row r="1603">
+      <c r="A1603" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1603" t="s" s="2">
+        <v>3247</v>
+      </c>
+      <c r="C1603" t="s" s="2">
+        <v>3248</v>
+      </c>
+      <c r="D1603" s="2"/>
+    </row>
+    <row r="1604">
+      <c r="A1604" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1604" t="s" s="2">
+        <v>3249</v>
+      </c>
+      <c r="C1604" t="s" s="2">
+        <v>3250</v>
+      </c>
+      <c r="D1604" s="2"/>
+    </row>
+    <row r="1605">
+      <c r="A1605" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1605" t="s" s="2">
+        <v>3251</v>
+      </c>
+      <c r="C1605" t="s" s="2">
+        <v>3252</v>
+      </c>
+      <c r="D1605" s="2"/>
+    </row>
+    <row r="1606">
+      <c r="A1606" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1606" t="s" s="2">
+        <v>3253</v>
+      </c>
+      <c r="C1606" t="s" s="2">
+        <v>3254</v>
+      </c>
+      <c r="D1606" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/www/terminologies/CodeSystem-terminologie-cisis.xlsx
+++ b/www/terminologies/CodeSystem-terminologie-cisis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4879" uniqueCount="3255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4882" uniqueCount="3257">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>202603110000</t>
+    <t>202604200000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:52:01-00:00</t>
+    <t>2026-04-20T11:06:51-00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -8561,6 +8561,12 @@
   </si>
   <si>
     <t>Questionnaire Mon Bilan Prévention 70-75 ans</t>
+  </si>
+  <si>
+    <t>MED-1350</t>
+  </si>
+  <si>
+    <t>Entrées/sorties hydro-électrolytiques</t>
   </si>
   <si>
     <t>ORG-001</t>
@@ -10180,7 +10186,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1606"/>
+  <dimension ref="A1:D1607"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -29457,6 +29463,18 @@
       </c>
       <c r="D1606" s="2"/>
     </row>
+    <row r="1607">
+      <c r="A1607" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1607" t="s" s="2">
+        <v>3255</v>
+      </c>
+      <c r="C1607" t="s" s="2">
+        <v>3256</v>
+      </c>
+      <c r="D1607" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/www/terminologies/CodeSystem-terminologie-cisis.xlsx
+++ b/www/terminologies/CodeSystem-terminologie-cisis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4882" uniqueCount="3257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4888" uniqueCount="3261">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>202604200000</t>
+    <t>202606190000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T11:06:51-00:00</t>
+    <t>2026-06-19T15:54:56-00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2668,7 +2668,7 @@
     <t>GEN-429</t>
   </si>
   <si>
-    <t>Nombre de kits</t>
+    <t>Nombre de kits salivaires</t>
   </si>
   <si>
     <t>GEN-430</t>
@@ -8567,6 +8567,18 @@
   </si>
   <si>
     <t>Entrées/sorties hydro-électrolytiques</t>
+  </si>
+  <si>
+    <t>MED-1351</t>
+  </si>
+  <si>
+    <t>Envoi kit salivaire au CNR</t>
+  </si>
+  <si>
+    <t>MED-1352</t>
+  </si>
+  <si>
+    <t>Envoi autres prélèvements au CNR</t>
   </si>
   <si>
     <t>ORG-001</t>
@@ -10186,7 +10198,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1607"/>
+  <dimension ref="A1:D1609"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -29475,6 +29487,30 @@
       </c>
       <c r="D1607" s="2"/>
     </row>
+    <row r="1608">
+      <c r="A1608" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1608" t="s" s="2">
+        <v>3257</v>
+      </c>
+      <c r="C1608" t="s" s="2">
+        <v>3258</v>
+      </c>
+      <c r="D1608" s="2"/>
+    </row>
+    <row r="1609">
+      <c r="A1609" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B1609" t="s" s="2">
+        <v>3259</v>
+      </c>
+      <c r="C1609" t="s" s="2">
+        <v>3260</v>
+      </c>
+      <c r="D1609" s="2"/>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/www/terminologies/CodeSystem-terminologie-cisis.xlsx
+++ b/www/terminologies/CodeSystem-terminologie-cisis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4888" uniqueCount="3261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4882" uniqueCount="3257">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>202606190000</t>
+    <t>202604200000</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T15:54:56-00:00</t>
+    <t>2026-04-20T11:06:51-00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2668,7 +2668,7 @@
     <t>GEN-429</t>
   </si>
   <si>
-    <t>Nombre de kits salivaires</t>
+    <t>Nombre de kits</t>
   </si>
   <si>
     <t>GEN-430</t>
@@ -8567,18 +8567,6 @@
   </si>
   <si>
     <t>Entrées/sorties hydro-électrolytiques</t>
-  </si>
-  <si>
-    <t>MED-1351</t>
-  </si>
-  <si>
-    <t>Envoi kit salivaire au CNR</t>
-  </si>
-  <si>
-    <t>MED-1352</t>
-  </si>
-  <si>
-    <t>Envoi autres prélèvements au CNR</t>
   </si>
   <si>
     <t>ORG-001</t>
@@ -10198,7 +10186,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D1609"/>
+  <dimension ref="A1:D1607"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -29487,30 +29475,6 @@
       </c>
       <c r="D1607" s="2"/>
     </row>
-    <row r="1608">
-      <c r="A1608" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B1608" t="s" s="2">
-        <v>3257</v>
-      </c>
-      <c r="C1608" t="s" s="2">
-        <v>3258</v>
-      </c>
-      <c r="D1608" s="2"/>
-    </row>
-    <row r="1609">
-      <c r="A1609" t="s" s="2">
-        <v>57</v>
-      </c>
-      <c r="B1609" t="s" s="2">
-        <v>3259</v>
-      </c>
-      <c r="C1609" t="s" s="2">
-        <v>3260</v>
-      </c>
-      <c r="D1609" s="2"/>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
